--- a/out/Attention-MambaAMT_repeat_3_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.85907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.45907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6077945103300888</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.85907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.85907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.245061653421726e-05</v>
+        <v>-0.0001636688423329033</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08323184297411629</v>
+        <v>-0.1880240643416861</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.85907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.85907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.45907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08330429359065043</v>
+        <v>-0.188187733184019</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.45907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0834528258383444</v>
+        <v>-0.1883137879814992</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.534088135883432</v>
+        <v>0.4532643439425449</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9857489147070535</v>
+        <v>0.7190851840419322</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03805366754672766</v>
+        <v>0.03229498934037318</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5269113779248127</v>
+        <v>0.3296837330214824</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06673316718898636</v>
+        <v>0.05663440771829058</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.622311345363547</v>
+        <v>0.4106467815298203</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08107260522358219</v>
+        <v>0.06880380512071571</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7177176630741839</v>
+        <v>0.4916152194077403</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02145400764533757</v>
+        <v>0.01820721072785435</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.85907883537967</v>
+        <v>2.191318200473974</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6794489405211387</v>
+        <v>0.4591376975131349</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01191945916743429</v>
+        <v>0.01011517986443328</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6818129465992909</v>
+        <v>0.4611432202020767</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02504282535217615</v>
+        <v>0.02125219340740914</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7199949747118163</v>
+        <v>0.4935469639441147</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009836184271179603</v>
+        <v>0.008346563713272774</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7146016285107729</v>
+        <v>0.4889688993407928</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.007003411454209289</v>
+        <v>0.005942576346077685</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.718768166641725</v>
+        <v>0.4925045229694499</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002752877024855403</v>
+        <v>0.002336004426809805</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7172664135287933</v>
+        <v>0.4912289591168826</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001561075777681621</v>
+        <v>0.001323698149962162</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7176327223403267</v>
+        <v>0.4915391706108593</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005915795691863147</v>
+        <v>0.0005011531384238221</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7172535537495178</v>
+        <v>0.4912163490656288</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002746439526277077</v>
+        <v>0.0002328074557778932</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7172108377267625</v>
+        <v>0.4911792755974589</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.753031238295475e-05</v>
+        <v>8.219113179022926e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.717131019817608</v>
+        <v>0.4911106509188076</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.505010235451714e-05</v>
+        <v>2.075723058958612e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7170839693790058</v>
+        <v>0.4910698911740857</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>7.878615294793062e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7170789455504606</v>
+        <v>0.4910648710687505</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.21904232466842e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7170751088823553</v>
+        <v>0.4910608530244068</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-1.195152058104458e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7170730406878516</v>
+        <v>0.491058418354216</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7170674490278434</v>
+        <v>0.4910529011122263</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7170611250338355</v>
+        <v>0.4910465771182184</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.207794510330089</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7170557572452571</v>
+        <v>0.49104120932964</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.45907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7170557939937487</v>
+        <v>0.4910412460781317</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6077945103300888</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7170559042392243</v>
+        <v>0.4910413563236073</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.45907883537967</v>
+        <v>2.791318200473974</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7170559777362079</v>
+        <v>0.4910414298205909</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.45907883537967</v>
+        <v>-0.4867320633075707</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.717056161478667</v>
+        <v>0.49104161356305</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7170577049153235</v>
+        <v>0.4910431569997065</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7170591748549966</v>
+        <v>0.4910446269393796</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.85907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7170604243037186</v>
+        <v>0.4910458763881016</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7170617839979159</v>
+        <v>0.4910472360822989</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7170595790884067</v>
+        <v>0.4910450311727896</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7170591748549966</v>
+        <v>0.4910446269393796</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7170583296396846</v>
+        <v>0.4910437817240677</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7170588808670619</v>
+        <v>0.4910443329514449</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7170585501306355</v>
+        <v>0.4910440022150185</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.717058256142701</v>
+        <v>0.491043708227084</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7170583296396846</v>
+        <v>0.4910437817240677</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7170578886577826</v>
+        <v>0.4910433407421657</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7170577784123071</v>
+        <v>0.4910432304966901</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7170577416638154</v>
+        <v>0.4910431937481984</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7170578886577826</v>
+        <v>0.4910433407421657</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7170574109273891</v>
+        <v>0.491042863011772</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7170583663881763</v>
+        <v>0.4910438184725593</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7170583296396846</v>
+        <v>0.4910437817240677</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7170579989032583</v>
+        <v>0.4910434509876412</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7170584398851602</v>
+        <v>0.4910438919695432</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.717057815160799</v>
+        <v>0.491043267245182</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7170576314183399</v>
+        <v>0.4910430835027229</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7170572271849299</v>
+        <v>0.4910426792693129</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.717056381969618</v>
+        <v>0.4910418340540009</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7170563452211263</v>
+        <v>0.4910417973055092</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7170564922150935</v>
+        <v>0.4910419442994765</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7170564187181099</v>
+        <v>0.4910418708024928</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7170564922150935</v>
+        <v>0.4910419442994765</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7170565289635854</v>
+        <v>0.4910419810479684</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7170564187181099</v>
+        <v>0.4910418708024928</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7170568597000118</v>
+        <v>0.4910423117843948</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7170567494545362</v>
+        <v>0.4910422015389193</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7170567127060443</v>
+        <v>0.4910421647904273</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7170566392090607</v>
+        <v>0.4910420912934437</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.717056602460569</v>
+        <v>0.491042054544952</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.717056381969618</v>
+        <v>0.4910418340540009</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7170563084726342</v>
+        <v>0.4910417605570173</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7170562349756506</v>
+        <v>0.4910416870600336</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.207794510330089</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7170562717241425</v>
+        <v>0.4910417238085256</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.45907883537967</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.717056161478667</v>
+        <v>0.49104161356305</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7170562717241425</v>
+        <v>0.4910417238085256</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-1.086732063307571</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7170565657120771</v>
+        <v>0.4910420177964601</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.389011768588428</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.45907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.45907883537967</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.85907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266862</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.245061653421726e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08323184297411629</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.85907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.85907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.45907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.45907883537967</v>
+        <v>1.640511201403203</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08330429359065043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0834528258383444</v>
+        <v>-0.0001236990921515972</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.534088135883432</v>
+        <v>0.444793764070519</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.9857489147070535</v>
+        <v>0.8903178493636916</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03805366754672766</v>
+        <v>0.03169146230293975</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5269113779248127</v>
+        <v>0.5081935118802587</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06673316718898636</v>
+        <v>0.05557602692903647</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.622311345363547</v>
+        <v>0.5876435272585091</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.08107260522358219</v>
+        <v>0.06751799745555123</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7177176630741839</v>
+        <v>0.6670988313008477</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02145400764533757</v>
+        <v>0.01786695380348709</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.85907883537967</v>
+        <v>0.7395115795266863</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6794489405211387</v>
+        <v>0.6352282448586118</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01191945916743429</v>
+        <v>0.00992587361792077</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.45907883537967</v>
+        <v>0.7395115795266862</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6818129465992909</v>
+        <v>0.6371961958237784</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02504282535217615</v>
+        <v>0.02085618023269161</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7199949747118163</v>
+        <v>0.6689949744665937</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009836184271179603</v>
+        <v>0.008190335215736203</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7146016285107729</v>
+        <v>0.6645024496934381</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.007003411454209289</v>
+        <v>0.005832180497426591</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.718768166641725</v>
+        <v>0.6679718491606156</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002752877024855403</v>
+        <v>0.002292551908446747</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7172664135287933</v>
+        <v>0.6667202295236886</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001561075777681621</v>
+        <v>0.001299035539290011</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7176327223403267</v>
+        <v>0.6670244098923471</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005915795691863147</v>
+        <v>0.0004917581845783683</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7172535537495178</v>
+        <v>0.6667078482507877</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002746439526277077</v>
+        <v>0.0002273026535608123</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7172108377267625</v>
+        <v>0.6666714437270269</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.753031238295475e-05</v>
+        <v>8.057648120152129e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.717131019817608</v>
+        <v>0.6666039972831656</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.505010235451714e-05</v>
+        <v>2.028024483792712e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7170839693790058</v>
+        <v>0.6665638997559387</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.45907883537967</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7170789455504606</v>
+        <v>0.6665588803952455</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.21904232466842e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7170751088823553</v>
+        <v>0.6665548623509018</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-1.195152058104458e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7170730406878516</v>
+        <v>0.666552427680711</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7170674490278434</v>
+        <v>0.6665469104387213</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7170611250338355</v>
+        <v>0.6665405864447134</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7170557572452571</v>
+        <v>0.6665352186561351</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.45907883537967</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7170557939937487</v>
+        <v>0.6665352554046268</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7170559042392243</v>
+        <v>0.6665353656501023</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266864</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7170559777362079</v>
+        <v>0.6665354391470859</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.45907883537967</v>
+        <v>0.9395115795266863</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.717056161478667</v>
+        <v>0.666535622889545</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7170577049153235</v>
+        <v>0.6665371663262015</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7170591748549966</v>
+        <v>0.6665386362658746</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.85907883537967</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7170604243037186</v>
+        <v>0.6665398857145967</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.03851195765016982</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7170617839979159</v>
+        <v>0.6665412454087939</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7170595790884067</v>
+        <v>0.6665390404992846</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7170591748549966</v>
+        <v>0.6665386362658746</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7170583296396846</v>
+        <v>0.6665377910505627</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7170588808670619</v>
+        <v>0.6665383422779398</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7170585501306355</v>
+        <v>0.6665380115415135</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.717058256142701</v>
+        <v>0.666537717553579</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7170583296396846</v>
+        <v>0.6665377910505627</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7170578886577826</v>
+        <v>0.6665373500686607</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7170577784123071</v>
+        <v>0.6665372398231851</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7170577416638154</v>
+        <v>0.6665372030746934</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7170578886577826</v>
+        <v>0.6665373500686607</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7170574109273891</v>
+        <v>0.6665368723382671</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7170583663881763</v>
+        <v>0.6665378277990543</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7170583296396846</v>
+        <v>0.6665377910505627</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7170579989032583</v>
+        <v>0.6665374603141362</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7170584398851602</v>
+        <v>0.6665379012960382</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.717057815160799</v>
+        <v>0.6665372765716771</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7170576314183399</v>
+        <v>0.6665370928292179</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7170572271849299</v>
+        <v>0.6665366885958078</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.717056381969618</v>
+        <v>0.6665358433804959</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7170563452211263</v>
+        <v>0.6665358066320042</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7170564922150935</v>
+        <v>0.6665359536259714</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7170564187181099</v>
+        <v>0.6665358801289878</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7170564922150935</v>
+        <v>0.6665359536259714</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7170565289635854</v>
+        <v>0.6665359903744634</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7170564187181099</v>
+        <v>0.6665358801289878</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7170568597000118</v>
+        <v>0.6665363211108898</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7170567494545362</v>
+        <v>0.6665362108654143</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7170567127060443</v>
+        <v>0.6665361741169223</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7170566392090607</v>
+        <v>0.6665361006199387</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.717056602460569</v>
+        <v>0.666536063871447</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.717056381969618</v>
+        <v>0.6665358433804959</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7170563084726342</v>
+        <v>0.6665357698835123</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.207794510330089</v>
+        <v>-0.6624876642263468</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7170562349756506</v>
+        <v>0.6665356963865287</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.207794510330089</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7170562717241425</v>
+        <v>0.6665357331350206</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.45907883537967</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.717056161478667</v>
+        <v>0.666535622889545</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6077945103300888</v>
+        <v>0.2385119576501699</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7170562717241425</v>
+        <v>0.6665357331350206</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6077945103300888</v>
+        <v>-0.4624876642263467</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7170565657120771</v>
+        <v>0.6665360271229551</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.00913558155298233</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.389011768588428</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01409348100423813</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.02000000000000024</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.05515133216977119</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9395115795266863</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01555429399013519</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.02167452871799469</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4624876642263467</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.01625895500183105</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004968944936990738</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003147691488265991</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0176260694861412</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.01339684426784515</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001707319170236588</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.03851195765016982</v>
+        <v>0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.006816763430833817</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0007280409336090088</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.00118439644575119</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01642362028360367</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9395115795266863</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0088629350066185</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.004714824259281158</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4624876642263467</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01040361076593399</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.003150857985019684</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.00395314022898674</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.005353901535272598</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.007095806300640106</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.003155186772346497</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002714846283197403</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.005069665610790253</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.002828966826200485</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4624876642263467</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.00829692929983139</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4624876642263467</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.005566269159317017</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0006699040532112122</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.03851195765016982</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.006100434809923172</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01168276742100716</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.9395115795266863</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.005086347460746765</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0002304799854755402</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002229701727628708</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.640511201403203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002995915710926056</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.005679529160261154</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003922052681446075</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001865707337856293</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.640511201403203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01399606093764305</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.640511201403203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01011542230844498</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.640511201403203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01966382935643196</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.640511201403203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.03568553179502487</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.03930608183145523</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7395115795266862</v>
+        <v>-0.16</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.003221258521080017</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-9.315708769287449e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.1070196012911481</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.02991359680891037</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.008315972983837128</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01161853224039078</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01311778277158737</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.008372209966182709</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.004124056547880173</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0009690038859844208</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02164899930357933</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01595857366919518</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.640511201403203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01214814931154251</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.00127854198217392</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.640511201403203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.01045472547411919</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.640511201403203</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02551988512277603</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.640511201403203</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>-0.1071127583788411</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01081881672143936</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9395115795266863</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.0001236990921515972</v>
+        <v>-0.107195290178011</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.444793764070519</v>
+        <v>0.2967655539730406</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.02962119877338409</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8903178493636916</v>
+        <v>0.4869056184988809</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03169146230293975</v>
+        <v>0.0211444468266281</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004194609820842743</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5081935118802587</v>
+        <v>0.2319529869918532</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05557602692903647</v>
+        <v>0.03708028369412986</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01081155985593796</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5876435272585091</v>
+        <v>0.2849619779636297</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06751799745555123</v>
+        <v>0.04504816554161525</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.03406183421611786</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6670988313008477</v>
+        <v>0.3379744971440681</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01786695380348709</v>
+        <v>0.0119208732929875</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.006115537136793137</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7395115795266863</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6352282448586118</v>
+        <v>0.3167105636086252</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00992587361792077</v>
+        <v>0.00662071862793783</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.001359641551971436</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7395115795266862</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6371961958237784</v>
+        <v>0.3180218968864733</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02085618023269161</v>
+        <v>0.01391396089809551</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.02695831656455994</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.2385119576501699</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6689949744665937</v>
+        <v>0.3392374891218566</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008190335215736203</v>
+        <v>0.005462997413779955</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.03202851861715317</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6645024496934381</v>
+        <v>0.336238264329596</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005832180497426591</v>
+        <v>0.003889903535221407</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02956940978765488</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6679718491606156</v>
+        <v>0.3385515840686287</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002292551908446747</v>
+        <v>0.001528059163496676</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02917719632387161</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6667202295236886</v>
+        <v>0.337714767537842</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001299035539290011</v>
+        <v>0.0008643570261933406</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02873963862657547</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6670244098923471</v>
+        <v>0.3379160715260736</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004917581845783683</v>
+        <v>0.0003261721230522456</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02757447212934494</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6667078482507877</v>
+        <v>0.3377029962801158</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002273026535608123</v>
+        <v>0.0001502354225216803</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02643901109695435</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6666714437270269</v>
+        <v>0.3376769859358545</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.057648120152129e-05</v>
+        <v>5.232009589913218e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03206021338701248</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6666039972831656</v>
+        <v>0.3376301586008151</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02087637037038803</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6665638997559387</v>
+        <v>0.3376016502520689</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.00558650866150856</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2385119576501699</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6665588803952455</v>
+        <v>0.3375966368485123</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01312686502933502</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.2385119576501699</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6665548623509018</v>
+        <v>0.337592291222703</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.009359650313854218</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4624876642263467</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.666552427680711</v>
+        <v>0.3375889408679101</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.03311119228601456</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4624876642263467</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6665469104387213</v>
+        <v>0.3375835715409224</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01425378769636154</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6665405864447134</v>
+        <v>0.3375775788074921</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02548713237047195</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6665352186561351</v>
+        <v>0.3375722110189137</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02032645791769028</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6665352554046268</v>
+        <v>0.3375722477674054</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01138515025377274</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6665353656501023</v>
+        <v>0.3375723580128809</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.009065229445695877</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9395115795266864</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6665354391470859</v>
+        <v>0.3375724315098645</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.02392872795462608</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9395115795266863</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.666535622889545</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.006048131734132767</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6665371663262015</v>
+        <v>0.3375741586889802</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01383352279663086</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2385119576501699</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6665386362658746</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01241767778992653</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.03851195765016982</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6665398857145967</v>
+        <v>0.3375768780773752</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.00644669309258461</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.03851195765016982</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6665412454087939</v>
+        <v>0.3375782377715725</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.03790123015642166</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6665390404992846</v>
+        <v>0.3375760328620633</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03133349120616913</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6665386362658746</v>
+        <v>0.3375756286286533</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0329134538769722</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6665377910505627</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02665399760007858</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6665383422779398</v>
+        <v>0.3375753346407185</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02684849500656128</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6665380115415135</v>
+        <v>0.3375750039042921</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02487841993570328</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.666537717553579</v>
+        <v>0.3375747099163576</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.03069507330656052</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6665377910505627</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02787402272224426</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6665373500686607</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01849467307329178</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6665372398231851</v>
+        <v>0.3375742321859638</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.02573356032371521</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6665372030746934</v>
+        <v>0.3375741954374721</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01624004542827606</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6665373500686607</v>
+        <v>0.3375743424314393</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01200148463249207</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6665368723382671</v>
+        <v>0.3375738647010457</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02771525830030441</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6665378277990543</v>
+        <v>0.337574820161833</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.03309711068868637</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6665377910505627</v>
+        <v>0.3375747834133413</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.02807058393955231</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6665374603141362</v>
+        <v>0.3375744526769149</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02709075063467026</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6665379012960382</v>
+        <v>0.3375748936588168</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02892627567052841</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6665372765716771</v>
+        <v>0.3375742689344557</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02958974987268448</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6665370928292179</v>
+        <v>0.3375740851919966</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0402396097779274</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6665366885958078</v>
+        <v>0.3375736809585865</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.04571863263845444</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6665358433804959</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01169545203447342</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6665358066320042</v>
+        <v>0.3375727989947828</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01196372509002686</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6665359536259714</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.009226419031620026</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6665358801289878</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.03577262908220291</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6665359536259714</v>
+        <v>0.3375729459887501</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02942443639039993</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6665359903744634</v>
+        <v>0.337572982737242</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01961874216794968</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6665358801289878</v>
+        <v>0.3375728724917665</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.02409342676401138</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6665363211108898</v>
+        <v>0.3375733134736684</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02589177340269089</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6624876642263468</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6665362108654143</v>
+        <v>0.3375732032281928</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01569632440805435</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6665361741169223</v>
+        <v>0.3375731664797009</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01929349452257156</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6665361006199387</v>
+        <v>0.3375730929827173</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02590002119541168</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.666536063871447</v>
+        <v>0.3375730562342256</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01808347553014755</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6665358433804959</v>
+        <v>0.3375728357432745</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.03118530660867691</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6665357698835123</v>
+        <v>0.3375727622462909</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.006031375378370285</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6624876642263468</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6665356963865287</v>
+        <v>0.3375726887493073</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.02699083834886551</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2385119576501699</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6665357331350206</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.003235843032598495</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.2385119576501699</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.666535622889545</v>
+        <v>0.3375726152523237</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01829039305448532</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2385119576501699</v>
+        <v>-0.5100000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6665357331350206</v>
+        <v>0.3375727254977992</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.04053955525159836</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4624876642263467</v>
+        <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6665360271229551</v>
+        <v>0.3375730194857337</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_3_000008.xlsx
+++ b/out/Attention-MambaAMT_repeat_3_000008.xlsx
@@ -16049,7 +16049,7 @@
         <v>-0.01040361076593399</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>-0.003150857985019684</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>-0.00395314022898674</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>-0.005353901535272598</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>-0.007095806300640106</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>-0.005566269159317017</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
